--- a/data/trending_integrated_20261007_09.xlsx
+++ b/data/trending_integrated_20261007_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47500</v>
+        <v>10700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+0.21%</t>
+          <t>'+10.65%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="E2" t="n">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>1072</v>
+        <v>203</v>
       </c>
       <c r="H2" t="n">
-        <v>14.12</v>
+        <v>5.01</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>47400</v>
+        <v>9670</v>
       </c>
       <c r="K2" t="n">
-        <v>46350</v>
+        <v>11020</v>
       </c>
       <c r="L2" t="n">
-        <v>47600</v>
+        <v>11030</v>
       </c>
       <c r="M2" t="n">
-        <v>45650</v>
+        <v>10590</v>
       </c>
       <c r="N2" t="n">
-        <v>14.1</v>
+        <v>4.84</v>
       </c>
       <c r="O2" t="n">
-        <v>3822423550</v>
+        <v>4713992130</v>
       </c>
       <c r="P2" t="n">
-        <v>69200</v>
+        <v>15900</v>
       </c>
       <c r="Q2" t="n">
-        <v>24150</v>
+        <v>6310</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB의 FDA 승인 기대감과 함께 공매도 세력에 대한 비판. 기타법인의 자사주 매집 및 긍정적 사업 전망 제시.</t>
+          <t>다양한 질병 테마에 대한 언급과 함께, 사망자 발생 소식 등 부정적인 뉴스도 존재하나 전반적인 기대감이 다소 높음. 페스트, 에볼라 관련 뉴스가 혼재됨.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 승인', '공매도', '자사주 매집']</t>
+          <t>['테마주', '사망자 발생', '질병']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>239500</v>
+        <v>248500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-0.62%</t>
+          <t>'+3.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>343</v>
+        <v>424</v>
       </c>
       <c r="H3" t="n">
         <v>4.12</v>
@@ -696,13 +696,13 @@
         <v>257000</v>
       </c>
       <c r="M3" t="n">
-        <v>239000</v>
+        <v>235000</v>
       </c>
       <c r="N3" t="n">
         <v>4.08</v>
       </c>
       <c r="O3" t="n">
-        <v>11375683500</v>
+        <v>38312322500</v>
       </c>
       <c r="P3" t="n">
         <v>1233000</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼천당제약의 경구용 인슐린 기술 이전 및 임상 결과 발표 예정에 대한 기대감. 공매도 세력과의 갈등 및 주가 변동성 우려 상존.</t>
+          <t>경구용 인슐린 10조 원대 L/O 예상 및 12월 임상 1차 결과 발표 예정 등 구체적인 호재가 언급되며, 거래량을 동반한 상승 기대감이 높음. 공매도 관련 비판도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['경구용 인슐린', '공매도', '임상 결과']</t>
+          <t>['경구용 인슐린', 'L/O', '임상 결과']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1735000</v>
+        <v>83000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'+1.84%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>655</v>
+        <v>106</v>
       </c>
       <c r="F4" t="n">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>2073</v>
+        <v>390</v>
       </c>
       <c r="H4" t="n">
-        <v>49.71</v>
+        <v>22.59</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1773000</v>
+        <v>81500</v>
       </c>
       <c r="K4" t="n">
-        <v>1728000</v>
+        <v>83500</v>
       </c>
       <c r="L4" t="n">
-        <v>1745000</v>
+        <v>84300</v>
       </c>
       <c r="M4" t="n">
-        <v>1725000</v>
+        <v>82800</v>
       </c>
       <c r="N4" t="n">
-        <v>49.76</v>
+        <v>22.56</v>
       </c>
       <c r="O4" t="n">
-        <v>337949224000</v>
+        <v>42487463200</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q4" t="n">
-        <v>403000</v>
+        <v>57000</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,27 +810,395 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 급락 및 관련 악재에 대한 투자자들의 불안감 고조. 솔리다임 상장 및 락업 해제 등 부정적 요인 언급.</t>
+          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 관련 뉴스가 긍정적인 전망을 뒷받침하며 상승 기대감을 높이고 있음.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['원전', '전력 구매 계약', '미국']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HLB제약</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>13070</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'+0.46%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F5" t="n">
+        <v>43</v>
+      </c>
+      <c r="G5" t="n">
+        <v>107</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>13010</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12330</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13560</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12260</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>18131021240</v>
+      </c>
+      <c r="P5" t="n">
+        <v>22250</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>기타법인의 자사주 매집 및 유증 물량 소화 관련 언급이 있으며, 비만 치료제 개발에 대한 기대감도 일부 존재함. 주가 조작 의혹 제기도 있음.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['자사주 매집', '유증', '비만 치료제']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>047920</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>273000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+0.37%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E6" t="n">
+        <v>480</v>
+      </c>
+      <c r="F6" t="n">
+        <v>312</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1768</v>
+      </c>
+      <c r="H6" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>272000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>269500</v>
+      </c>
+      <c r="L6" t="n">
+        <v>274000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>268500</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="O6" t="n">
+        <v>316693922250</v>
+      </c>
+      <c r="P6" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>90200</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 관련된 언급이 주를 이루며, 실적 발표에 대한 기대감도 일부 존재함.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
         <v>0.1</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['정치', '실적', '기대감']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>47350</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-0.11%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E7" t="n">
+        <v>146</v>
+      </c>
+      <c r="F7" t="n">
+        <v>110</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1113</v>
+      </c>
+      <c r="H7" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>47400</v>
+      </c>
+      <c r="K7" t="n">
+        <v>46350</v>
+      </c>
+      <c r="L7" t="n">
+        <v>47850</v>
+      </c>
+      <c r="M7" t="n">
+        <v>45650</v>
+      </c>
+      <c r="N7" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>13006704700</v>
+      </c>
+      <c r="P7" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>FDA 승인 가능성 90% 이상의 긍정적 전망과 함께, 기타법인의 자사주 매집 소식이 호재로 작용하며 기대감을 높이고 있음. 공매도 관련 언급도 다수.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['FDA 승인', '자사주 매집', '공매도']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1743000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-1.69%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E8" t="n">
+        <v>712</v>
+      </c>
+      <c r="F8" t="n">
+        <v>435</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2147</v>
+      </c>
+      <c r="H8" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1773000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1728000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1745000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1725000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="O8" t="n">
+        <v>591009818500</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SK하이닉스 ADR 급락 및 관련 악재에 대한 투자자들의 불안감 고조. 솔리다임 상장 및 락업 해제 등 부정적 요인 언급.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>['ADR', '락업 해제', '솔리다임']</t>
         </is>
       </c>
-      <c r="X4" t="n">
+      <c r="X8" t="n">
         <v>7</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261007_09.xlsx
+++ b/data/trending_integrated_20261007_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10700</v>
+        <v>10490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+10.65%</t>
+          <t>'+8.48%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.17</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="H2" t="n">
         <v>5.01</v>
@@ -604,13 +604,13 @@
         <v>11030</v>
       </c>
       <c r="M2" t="n">
-        <v>10590</v>
+        <v>10420</v>
       </c>
       <c r="N2" t="n">
         <v>4.84</v>
       </c>
       <c r="O2" t="n">
-        <v>4713992130</v>
+        <v>6843134345</v>
       </c>
       <c r="P2" t="n">
         <v>15900</v>
@@ -619,23 +619,23 @@
         <v>6310</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-113000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>다양한 질병 테마에 대한 언급과 함께, 사망자 발생 소식 등 부정적인 뉴스도 존재하나 전반적인 기대감이 다소 높음. 페스트, 에볼라 관련 뉴스가 혼재됨.</t>
+          <t>각종 질병 테마주로서의 기대와 관련 뉴스가 혼재된 게시글, 감정적 반응이 주를 이룸.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['테마주', '사망자 발생', '질병']</t>
+          <t>['테마주', '백신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>248500</v>
+        <v>278250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+3.11%</t>
+          <t>'+2.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>552</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>356</v>
       </c>
       <c r="G3" t="n">
-        <v>424</v>
+        <v>1912</v>
       </c>
       <c r="H3" t="n">
-        <v>4.12</v>
+        <v>46.37</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>241000</v>
+        <v>272000</v>
       </c>
       <c r="K3" t="n">
-        <v>253000</v>
+        <v>269500</v>
       </c>
       <c r="L3" t="n">
-        <v>257000</v>
+        <v>278500</v>
       </c>
       <c r="M3" t="n">
-        <v>235000</v>
+        <v>268500</v>
       </c>
       <c r="N3" t="n">
-        <v>4.08</v>
+        <v>46.41</v>
       </c>
       <c r="O3" t="n">
-        <v>38312322500</v>
+        <v>675342827750</v>
       </c>
       <c r="P3" t="n">
-        <v>1233000</v>
+        <v>374500</v>
       </c>
       <c r="Q3" t="n">
-        <v>120000</v>
+        <v>90200</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>359000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조 원대 L/O 예상 및 12월 임상 1차 결과 발표 예정 등 구체적인 호재가 언급되며, 거래량을 동반한 상승 기대감이 높음. 공매도 관련 비판도 존재.</t>
+          <t>정치 관련 이슈와 함께 삼성전자 주가 하락에 대한 부정적 전망이 혼재된 게시글.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['경구용 인슐린', 'L/O', '임상 결과']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83000</v>
+        <v>245000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.84%</t>
+          <t>'+1.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>390</v>
+        <v>479</v>
       </c>
       <c r="H4" t="n">
-        <v>22.59</v>
+        <v>4.12</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>81500</v>
+        <v>241000</v>
       </c>
       <c r="K4" t="n">
-        <v>83500</v>
+        <v>253000</v>
       </c>
       <c r="L4" t="n">
-        <v>84300</v>
+        <v>257000</v>
       </c>
       <c r="M4" t="n">
-        <v>82800</v>
+        <v>235000</v>
       </c>
       <c r="N4" t="n">
-        <v>22.56</v>
+        <v>4.08</v>
       </c>
       <c r="O4" t="n">
-        <v>42487463200</v>
+        <v>44496598750</v>
       </c>
       <c r="P4" t="n">
-        <v>139200</v>
+        <v>1233000</v>
       </c>
       <c r="Q4" t="n">
-        <v>57000</v>
+        <v>120000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-43000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 관련 뉴스가 긍정적인 전망을 뒷받침하며 상승 기대감을 높이고 있음.</t>
+          <t>경구용 인슐린 기술 수출(L/O) 기대감과 임상 결과 발표 예정 등 긍정적 전망을 기반으로 한 상승세 예측.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전', '전력 구매 계약', '미국']</t>
+          <t>['경구용 인슐린', '기술수출']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13070</v>
+        <v>82200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'+0.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.88</v>
+        <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="G5" t="n">
-        <v>107</v>
+        <v>441</v>
       </c>
       <c r="H5" t="n">
-        <v>1.42</v>
+        <v>22.59</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13010</v>
+        <v>81500</v>
       </c>
       <c r="K5" t="n">
-        <v>12330</v>
+        <v>83500</v>
       </c>
       <c r="L5" t="n">
-        <v>13560</v>
+        <v>84300</v>
       </c>
       <c r="M5" t="n">
-        <v>12260</v>
+        <v>81700</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>22.56</v>
       </c>
       <c r="O5" t="n">
-        <v>18131021240</v>
+        <v>62673209950</v>
       </c>
       <c r="P5" t="n">
-        <v>22250</v>
+        <v>139200</v>
       </c>
       <c r="Q5" t="n">
-        <v>6000</v>
+        <v>57000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>143000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>기타법인의 자사주 매집 및 유증 물량 소화 관련 언급이 있으며, 비만 치료제 개발에 대한 기대감도 일부 존재함. 주가 조작 의혹 제기도 있음.</t>
+          <t>미국 원전주 급등에 따른 기대감과 구글의 전력구매 계약 소식을 기반으로 한 상승 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주 매집', '유증', '비만 치료제']</t>
+          <t>['원전주', '전력구매']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>273000</v>
+        <v>18560</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.37%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>1.11</v>
       </c>
       <c r="E6" t="n">
-        <v>480</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>312</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>1768</v>
+        <v>439</v>
       </c>
       <c r="H6" t="n">
-        <v>46.37</v>
+        <v>4.92</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>272000</v>
+        <v>18530</v>
       </c>
       <c r="K6" t="n">
-        <v>269500</v>
+        <v>18950</v>
       </c>
       <c r="L6" t="n">
-        <v>274000</v>
+        <v>19870</v>
       </c>
       <c r="M6" t="n">
-        <v>268500</v>
+        <v>18360</v>
       </c>
       <c r="N6" t="n">
-        <v>46.41</v>
+        <v>3.81</v>
       </c>
       <c r="O6" t="n">
-        <v>316693922250</v>
+        <v>168129982860</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>90200</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 언급이 주를 이루며, 실적 발표에 대한 기대감도 일부 존재함.</t>
+          <t>미국 광통신 주가 상승 및 젠슨황의 광통신 지지 등 긍정적 요인이 있으나, 명확한 분석 없이 감정적 반응만 나타남.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['정치', '실적', '기대감']</t>
+          <t>['광통신', '젠슨황']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47350</v>
+        <v>1763000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.11%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>146</v>
+        <v>761</v>
       </c>
       <c r="F7" t="n">
-        <v>110</v>
+        <v>457</v>
       </c>
       <c r="G7" t="n">
-        <v>1113</v>
+        <v>2205</v>
       </c>
       <c r="H7" t="n">
-        <v>14.12</v>
+        <v>49.71</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>47400</v>
+        <v>1773000</v>
       </c>
       <c r="K7" t="n">
-        <v>46350</v>
+        <v>1728000</v>
       </c>
       <c r="L7" t="n">
-        <v>47850</v>
+        <v>1765000</v>
       </c>
       <c r="M7" t="n">
-        <v>45650</v>
+        <v>1725000</v>
       </c>
       <c r="N7" t="n">
-        <v>14.1</v>
+        <v>49.76</v>
       </c>
       <c r="O7" t="n">
-        <v>13006704700</v>
+        <v>861419058000</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>403000</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-102000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상의 긍정적 전망과 함께, 기타법인의 자사주 매집 소식이 호재로 작용하며 기대감을 높이고 있음. 공매도 관련 언급도 다수.</t>
+          <t>SK하이닉스 ADR 급락 및 관련 악재에 대한 투자자들의 불안감 고조. 솔리다임 상장 및 락업 해제 등 부정적 요인 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FDA 승인', '자사주 매집', '공매도']</t>
+          <t>['ADR', '락업 해제', '솔리다임']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,99 +1108,191 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1743000</v>
+        <v>46950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'-0.95%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>712</v>
+        <v>163</v>
       </c>
       <c r="F8" t="n">
-        <v>435</v>
+        <v>120</v>
       </c>
       <c r="G8" t="n">
-        <v>2147</v>
+        <v>1212</v>
       </c>
       <c r="H8" t="n">
-        <v>49.71</v>
+        <v>14.12</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1773000</v>
+        <v>47400</v>
       </c>
       <c r="K8" t="n">
-        <v>1728000</v>
+        <v>46350</v>
       </c>
       <c r="L8" t="n">
-        <v>1745000</v>
+        <v>47850</v>
       </c>
       <c r="M8" t="n">
-        <v>1725000</v>
+        <v>45650</v>
       </c>
       <c r="N8" t="n">
-        <v>49.76</v>
+        <v>14.1</v>
       </c>
       <c r="O8" t="n">
-        <v>591009818500</v>
+        <v>16764335350</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>403000</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 급락 및 관련 악재에 대한 투자자들의 불안감 고조. 솔리다임 상장 및 락업 해제 등 부정적 요인 언급.</t>
+          <t>FDA 승인 가능성 90% 이상의 긍정적 전망과 함께, 기타법인의 자사주 매집 소식이 호재로 작용하며 기대감을 높이고 있음. 공매도 관련 언급도 다수.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['FDA 승인', '자사주 매집', '공매도']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HLB제약</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12730</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-2.15%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E9" t="n">
+        <v>54</v>
+      </c>
+      <c r="F9" t="n">
+        <v>45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>115</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>13010</v>
+      </c>
+      <c r="K9" t="n">
+        <v>12330</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13560</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12260</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>22555933685</v>
+      </c>
+      <c r="P9" t="n">
+        <v>22250</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-24000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>유증 물량 부담과 신규 상장 이슈로 인한 하락 가능성, 주가 조작 의혹 등 부정적 의견이 혼재.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
         <v>0.1</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>['ADR', '락업 해제', '솔리다임']</t>
-        </is>
-      </c>
-      <c r="X8" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['유증', '신규상장']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>000660</t>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>047920</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261007_09.xlsx
+++ b/data/trending_integrated_20261007_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10490</v>
+        <v>10730</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+10.96%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.17</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="H2" t="n">
         <v>5.01</v>
@@ -610,7 +610,7 @@
         <v>4.84</v>
       </c>
       <c r="O2" t="n">
-        <v>6843134345</v>
+        <v>8117361640</v>
       </c>
       <c r="P2" t="n">
         <v>15900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>각종 질병 테마주로서의 기대와 관련 뉴스가 혼재된 게시글, 감정적 반응이 주를 이룸.</t>
+          <t>에볼라, 페스트 등 전염병 테마주로 부각. 사망자 발생 소식과 백신 관련 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['테마주', '백신']</t>
+          <t>['전염병', '백신', '테마주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>278250</v>
+        <v>15590</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+2.30%</t>
+          <t>'+4.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.04</v>
+        <v>0.98</v>
       </c>
       <c r="E3" t="n">
-        <v>552</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
-        <v>356</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>1912</v>
+        <v>92</v>
       </c>
       <c r="H3" t="n">
-        <v>46.37</v>
+        <v>2.37</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>272000</v>
+        <v>14870</v>
       </c>
       <c r="K3" t="n">
-        <v>269500</v>
+        <v>15480</v>
       </c>
       <c r="L3" t="n">
-        <v>278500</v>
+        <v>16960</v>
       </c>
       <c r="M3" t="n">
-        <v>268500</v>
+        <v>14600</v>
       </c>
       <c r="N3" t="n">
-        <v>46.41</v>
+        <v>1.39</v>
       </c>
       <c r="O3" t="n">
-        <v>675342827750</v>
+        <v>102397792490</v>
       </c>
       <c r="P3" t="n">
-        <v>374500</v>
+        <v>16960</v>
       </c>
       <c r="Q3" t="n">
-        <v>90200</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>359000</v>
+        <v>-75000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정치 관련 이슈와 함께 삼성전자 주가 하락에 대한 부정적 전망이 혼재된 게시글.</t>
+          <t>개인정보 유출 사건 발생 속 양자보안 부각. 농협, KDB생명 등 해킹 방어 및 다수 기업 공급 논의.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['양자보안', '해킹', '개인정보']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>245000</v>
+        <v>250500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.66%</t>
+          <t>'+3.94%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
         <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="H4" t="n">
         <v>4.12</v>
@@ -794,7 +794,7 @@
         <v>4.08</v>
       </c>
       <c r="O4" t="n">
-        <v>44496598750</v>
+        <v>48564187000</v>
       </c>
       <c r="P4" t="n">
         <v>1233000</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>경구용 인슐린 기술 수출(L/O) 기대감과 임상 결과 발표 예정 등 긍정적 전망을 기반으로 한 상승세 예측.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 12월 임상 1차 결과 발표 예정. 공매도 세력과의 갈등.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['경구용 인슐린', '기술수출']</t>
+          <t>['경구용 인슐린', 'L/O', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82200</v>
+        <v>278250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.86%</t>
+          <t>'+2.30%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>134</v>
+        <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>95</v>
+        <v>380</v>
       </c>
       <c r="G5" t="n">
-        <v>441</v>
+        <v>1999</v>
       </c>
       <c r="H5" t="n">
-        <v>22.59</v>
+        <v>46.37</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>81500</v>
+        <v>272000</v>
       </c>
       <c r="K5" t="n">
-        <v>83500</v>
+        <v>269500</v>
       </c>
       <c r="L5" t="n">
-        <v>84300</v>
+        <v>278500</v>
       </c>
       <c r="M5" t="n">
-        <v>81700</v>
+        <v>268500</v>
       </c>
       <c r="N5" t="n">
-        <v>22.56</v>
+        <v>46.41</v>
       </c>
       <c r="O5" t="n">
-        <v>62673209950</v>
+        <v>830436745250</v>
       </c>
       <c r="P5" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>57000</v>
+        <v>90200</v>
       </c>
       <c r="R5" t="n">
-        <v>143000</v>
+        <v>359000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 원전주 급등에 따른 기대감과 구글의 전력구매 계약 소식을 기반으로 한 상승 전망.</t>
+          <t>정치 관련 이슈와 함께 삼성전자 주가 하락에 대한 부정적 전망이 혼재된 게시글.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전주', '전력구매']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18560</v>
+        <v>18810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'+1.51%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.11</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>439</v>
+        <v>494</v>
       </c>
       <c r="H6" t="n">
         <v>4.92</v>
@@ -978,7 +978,7 @@
         <v>3.81</v>
       </c>
       <c r="O6" t="n">
-        <v>168129982860</v>
+        <v>183161456620</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨황의 광통신 지지 등 긍정적 요인이 있으나, 명확한 분석 없이 감정적 반응만 나타남.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 뉴스. 신고가 돌파 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '젠슨황']</t>
+          <t>['광통신', '신고가', '젠슨 황']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1763000</v>
+        <v>82000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'+0.61%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>761</v>
+        <v>153</v>
       </c>
       <c r="F7" t="n">
-        <v>457</v>
+        <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>2205</v>
+        <v>450</v>
       </c>
       <c r="H7" t="n">
-        <v>49.71</v>
+        <v>22.59</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1773000</v>
+        <v>81500</v>
       </c>
       <c r="K7" t="n">
-        <v>1728000</v>
+        <v>83500</v>
       </c>
       <c r="L7" t="n">
-        <v>1765000</v>
+        <v>84300</v>
       </c>
       <c r="M7" t="n">
-        <v>1725000</v>
+        <v>81700</v>
       </c>
       <c r="N7" t="n">
-        <v>49.76</v>
+        <v>22.56</v>
       </c>
       <c r="O7" t="n">
-        <v>861419058000</v>
+        <v>68766757000</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>403000</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>-102000</v>
+        <v>143000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 급락 및 관련 악재에 대한 투자자들의 불안감 고조. 솔리다임 상장 및 락업 해제 등 부정적 요인 언급.</t>
+          <t>구글의 미국 원전 기업 컨스텔레이션 전력구매 계약 관련 호재. 공매도 청산 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['ADR', '락업 해제', '솔리다임']</t>
+          <t>['원전', '구글', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46950</v>
+        <v>1771000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.95%</t>
+          <t>'-0.11%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>163</v>
+        <v>795</v>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>470</v>
       </c>
       <c r="G8" t="n">
-        <v>1212</v>
+        <v>2252</v>
       </c>
       <c r="H8" t="n">
-        <v>14.12</v>
+        <v>49.71</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47400</v>
+        <v>1773000</v>
       </c>
       <c r="K8" t="n">
-        <v>46350</v>
+        <v>1728000</v>
       </c>
       <c r="L8" t="n">
-        <v>47850</v>
+        <v>1772000</v>
       </c>
       <c r="M8" t="n">
-        <v>45650</v>
+        <v>1725000</v>
       </c>
       <c r="N8" t="n">
-        <v>14.1</v>
+        <v>49.76</v>
       </c>
       <c r="O8" t="n">
-        <v>16764335350</v>
+        <v>983732058500</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>403000</v>
       </c>
       <c r="R8" t="n">
-        <v>-8000</v>
+        <v>-102000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상의 긍정적 전망과 함께, 기타법인의 자사주 매집 소식이 호재로 작용하며 기대감을 높이고 있음. 공매도 관련 언급도 다수.</t>
+          <t>SK하이닉스 ADR 급락 및 관련 악재에 대한 투자자들의 불안감 고조. 솔리다임 상장 및 락업 해제 등 부정적 요인 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA 승인', '자사주 매집', '공매도']</t>
+          <t>['ADR', '락업 해제', '솔리다임']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12730</v>
+        <v>12830</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1.88</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H9" t="n">
         <v>1.42</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>22555933685</v>
+        <v>24075058005</v>
       </c>
       <c r="P9" t="n">
         <v>22250</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유증 물량 부담과 신규 상장 이슈로 인한 하락 가능성, 주가 조작 의혹 등 부정적 의견이 혼재.</t>
+          <t>기타법인의 자사주 매집 및 유증 물량 소화 중. 담관암 치료제 개발 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유증', '신규상장']</t>
+          <t>['유증', '자사주', '담관암']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1293,6 +1293,190 @@
       <c r="Z9" t="inlineStr">
         <is>
           <t>047920</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>46700</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-1.48%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E10" t="n">
+        <v>174</v>
+      </c>
+      <c r="F10" t="n">
+        <v>126</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1246</v>
+      </c>
+      <c r="H10" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>47400</v>
+      </c>
+      <c r="K10" t="n">
+        <v>46350</v>
+      </c>
+      <c r="L10" t="n">
+        <v>47850</v>
+      </c>
+      <c r="M10" t="n">
+        <v>45650</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>18633890300</v>
+      </c>
+      <c r="P10" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>FDA 승인 가능성 90% 이상 전망 및 담관암 매출 기대. 공매도 세력과의 갈등.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['FDA', '공매도', '담관암']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>30800</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-2.99%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>86</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>31750</v>
+      </c>
+      <c r="K11" t="n">
+        <v>32600</v>
+      </c>
+      <c r="L11" t="n">
+        <v>32850</v>
+      </c>
+      <c r="M11" t="n">
+        <v>30750</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="O11" t="n">
+        <v>48754723325</v>
+      </c>
+      <c r="P11" t="n">
+        <v>75900</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>15960</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-103000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>가온전선 대비 극심한 주가 부진 및 외국인/기관 매도세 지속. 소송 및 승계 작업 관련 루머.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['가온전선', '외국인', '기관']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>001440</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261007_09.xlsx
+++ b/data/trending_integrated_20261007_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10730</v>
+        <v>26500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+10.96%</t>
+          <t>'+15.47%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>232</v>
+        <v>102</v>
       </c>
       <c r="H2" t="n">
-        <v>5.01</v>
+        <v>2.82</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9670</v>
+        <v>22950</v>
       </c>
       <c r="K2" t="n">
-        <v>11020</v>
+        <v>26200</v>
       </c>
       <c r="L2" t="n">
-        <v>11030</v>
+        <v>27600</v>
       </c>
       <c r="M2" t="n">
-        <v>10420</v>
+        <v>25550</v>
       </c>
       <c r="N2" t="n">
-        <v>4.84</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>8117361640</v>
+        <v>54827897850</v>
       </c>
       <c r="P2" t="n">
-        <v>15900</v>
+        <v>30100</v>
       </c>
       <c r="Q2" t="n">
-        <v>6310</v>
+        <v>11140</v>
       </c>
       <c r="R2" t="n">
-        <v>-113000</v>
+        <v>141000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>에볼라, 페스트 등 전염병 테마주로 부각. 사망자 발생 소식과 백신 관련 기대감.</t>
+          <t>유리기판 관련 기술 및 주가 상승 기대감, 유상증자에 대한 논란.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['전염병', '백신', '테마주']</t>
+          <t>['유리기판', '유상증자']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15590</v>
+        <v>5520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+4.84%</t>
+          <t>'+10.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.98</v>
+        <v>3.32</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
         <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H3" t="n">
-        <v>2.37</v>
+        <v>4.72</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14870</v>
+        <v>5010</v>
       </c>
       <c r="K3" t="n">
-        <v>15480</v>
+        <v>5120</v>
       </c>
       <c r="L3" t="n">
-        <v>16960</v>
+        <v>5990</v>
       </c>
       <c r="M3" t="n">
-        <v>14600</v>
+        <v>4950</v>
       </c>
       <c r="N3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O3" t="n">
-        <v>102397792490</v>
+        <v>125355744635</v>
       </c>
       <c r="P3" t="n">
-        <v>16960</v>
+        <v>8100</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>592</v>
       </c>
       <c r="R3" t="n">
-        <v>-75000</v>
+        <v>908000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>개인정보 유출 사건 발생 속 양자보안 부각. 농협, KDB생명 등 해킹 방어 및 다수 기업 공급 논의.</t>
+          <t>기타법인 자사주 매집, 수주 계약 규모 언급 및 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', '해킹', '개인정보']</t>
+          <t>['자사주 매집', '수주 계약']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>250500</v>
+        <v>10560</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.94%</t>
+          <t>'+9.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>485</v>
+        <v>222</v>
       </c>
       <c r="H4" t="n">
-        <v>4.12</v>
+        <v>5.01</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>241000</v>
+        <v>9670</v>
       </c>
       <c r="K4" t="n">
-        <v>253000</v>
+        <v>11020</v>
       </c>
       <c r="L4" t="n">
-        <v>257000</v>
+        <v>11030</v>
       </c>
       <c r="M4" t="n">
-        <v>235000</v>
+        <v>10420</v>
       </c>
       <c r="N4" t="n">
-        <v>4.08</v>
+        <v>4.84</v>
       </c>
       <c r="O4" t="n">
-        <v>48564187000</v>
+        <v>8870044365</v>
       </c>
       <c r="P4" t="n">
-        <v>1233000</v>
+        <v>15900</v>
       </c>
       <c r="Q4" t="n">
-        <v>120000</v>
+        <v>6310</v>
       </c>
       <c r="R4" t="n">
-        <v>-43000</v>
+        <v>-113000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상 및 12월 임상 1차 결과 발표 예정. 공매도 세력과의 갈등.</t>
+          <t>다양한 질병 테마주 언급, 페스트 확산 관련 소식.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['경구용 인슐린', 'L/O', '공매도']</t>
+          <t>['테마주', '질병 확산']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>278250</v>
+        <v>15870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.30%</t>
+          <t>'+6.72%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>600</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>380</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>1999</v>
+        <v>99</v>
       </c>
       <c r="H5" t="n">
-        <v>46.37</v>
+        <v>2.37</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>272000</v>
+        <v>14870</v>
       </c>
       <c r="K5" t="n">
-        <v>269500</v>
+        <v>15480</v>
       </c>
       <c r="L5" t="n">
-        <v>278500</v>
+        <v>16960</v>
       </c>
       <c r="M5" t="n">
-        <v>268500</v>
+        <v>14600</v>
       </c>
       <c r="N5" t="n">
-        <v>46.41</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>830436745250</v>
+        <v>112110187605</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>16960</v>
       </c>
       <c r="Q5" t="n">
-        <v>90200</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>359000</v>
+        <v>-75000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치 관련 이슈와 함께 삼성전자 주가 하락에 대한 부정적 전망이 혼재된 게시글.</t>
+          <t>개인정보 유출 해킹 사건과 연관된 보안주 상승, 양자보안 기술 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['해킹', '보안주']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18810</v>
+        <v>279000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.51%</t>
+          <t>'+2.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.11</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>661</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>410</v>
       </c>
       <c r="G6" t="n">
-        <v>494</v>
+        <v>2059</v>
       </c>
       <c r="H6" t="n">
-        <v>4.92</v>
+        <v>46.37</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18530</v>
+        <v>272000</v>
       </c>
       <c r="K6" t="n">
-        <v>18950</v>
+        <v>269500</v>
       </c>
       <c r="L6" t="n">
-        <v>19870</v>
+        <v>279000</v>
       </c>
       <c r="M6" t="n">
-        <v>18360</v>
+        <v>268500</v>
       </c>
       <c r="N6" t="n">
-        <v>3.81</v>
+        <v>46.41</v>
       </c>
       <c r="O6" t="n">
-        <v>183161456620</v>
+        <v>1022159316250</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>90200</v>
       </c>
       <c r="R6" t="n">
-        <v>49000</v>
+        <v>359000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨 황의 광통신 지지 뉴스. 신고가 돌파 기대.</t>
+          <t>이유 없는 하락 예측 및 정치적 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '신고가', '젠슨 황']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82000</v>
+        <v>82200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.61%</t>
+          <t>'+0.86%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G7" t="n">
-        <v>450</v>
+        <v>481</v>
       </c>
       <c r="H7" t="n">
         <v>22.59</v>
@@ -1070,7 +1070,7 @@
         <v>22.56</v>
       </c>
       <c r="O7" t="n">
-        <v>68766757000</v>
+        <v>75084859550</v>
       </c>
       <c r="P7" t="n">
         <v>139200</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>구글의 미국 원전 기업 컨스텔레이션 전력구매 계약 관련 호재. 공매도 청산 기대감.</t>
+          <t>미국 원전주 급등에 따른 기대감, 구글 계약 호재 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '구글', '공매도']</t>
+          <t>['원전', '구글 계약']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1771000</v>
+        <v>242000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.11%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>795</v>
+        <v>102</v>
       </c>
       <c r="F8" t="n">
-        <v>470</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
-        <v>2252</v>
+        <v>512</v>
       </c>
       <c r="H8" t="n">
-        <v>49.71</v>
+        <v>4.12</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1773000</v>
+        <v>241000</v>
       </c>
       <c r="K8" t="n">
-        <v>1728000</v>
+        <v>253000</v>
       </c>
       <c r="L8" t="n">
-        <v>1772000</v>
+        <v>257000</v>
       </c>
       <c r="M8" t="n">
-        <v>1725000</v>
+        <v>235000</v>
       </c>
       <c r="N8" t="n">
-        <v>49.76</v>
+        <v>4.08</v>
       </c>
       <c r="O8" t="n">
-        <v>983732058500</v>
+        <v>52941309750</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>1233000</v>
       </c>
       <c r="Q8" t="n">
-        <v>403000</v>
+        <v>120000</v>
       </c>
       <c r="R8" t="n">
-        <v>-102000</v>
+        <v>-43000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 급락 및 관련 악재에 대한 투자자들의 불안감 고조. 솔리다임 상장 및 락업 해제 등 부정적 요인 언급.</t>
+          <t>경구용 인슐린 10조원대 LO 예상 및 12월 임상 1차 결과 발표 예정. 아일리아 이슈와 더불어 외국인 수급 동향 주목.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['ADR', '락업 해제', '솔리다임']</t>
+          <t>['경구용 인슐린', '임상 1차', '외국인 수급']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12830</v>
+        <v>1770000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-0.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.88</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>459</v>
       </c>
       <c r="G9" t="n">
-        <v>117</v>
+        <v>2143</v>
       </c>
       <c r="H9" t="n">
-        <v>1.42</v>
+        <v>49.71</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13010</v>
+        <v>1773000</v>
       </c>
       <c r="K9" t="n">
-        <v>12330</v>
+        <v>1728000</v>
       </c>
       <c r="L9" t="n">
-        <v>13560</v>
+        <v>1779000</v>
       </c>
       <c r="M9" t="n">
-        <v>12260</v>
+        <v>1725000</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>49.76</v>
       </c>
       <c r="O9" t="n">
-        <v>24075058005</v>
+        <v>1207599985500</v>
       </c>
       <c r="P9" t="n">
-        <v>22250</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>6000</v>
+        <v>403000</v>
       </c>
       <c r="R9" t="n">
-        <v>-24000</v>
+        <v>-102000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기타법인의 자사주 매집 및 유증 물량 소화 중. 담관암 치료제 개발 기대감.</t>
+          <t>ADR 급락에 따른 주가 하락 우려, 외국인 매도세 지적.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유증', '자사주', '담관암']</t>
+          <t>['ADR', '외국인 매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46700</v>
+        <v>18480</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.48%</t>
+          <t>'-0.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>1.11</v>
       </c>
       <c r="E10" t="n">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="F10" t="n">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="G10" t="n">
-        <v>1246</v>
+        <v>548</v>
       </c>
       <c r="H10" t="n">
-        <v>14.12</v>
+        <v>4.92</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47400</v>
+        <v>18530</v>
       </c>
       <c r="K10" t="n">
-        <v>46350</v>
+        <v>18950</v>
       </c>
       <c r="L10" t="n">
-        <v>47850</v>
+        <v>19870</v>
       </c>
       <c r="M10" t="n">
-        <v>45650</v>
+        <v>18360</v>
       </c>
       <c r="N10" t="n">
-        <v>14.1</v>
+        <v>3.81</v>
       </c>
       <c r="O10" t="n">
-        <v>18633890300</v>
+        <v>196214983890</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>1272</v>
       </c>
       <c r="R10" t="n">
-        <v>-8000</v>
+        <v>49000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상 전망 및 담관암 매출 기대. 공매도 세력과의 갈등.</t>
+          <t>미국 광통신 주가 상승 및 젠슨 황의 지지에 따른 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA', '공매도', '담관암']</t>
+          <t>['광통신', '젠슨 황']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,99 +1384,283 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30800</v>
+        <v>46100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.99%</t>
+          <t>'-2.74%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="G11" t="n">
-        <v>86</v>
+        <v>1281</v>
       </c>
       <c r="H11" t="n">
-        <v>10.78</v>
+        <v>14.12</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>31750</v>
+        <v>47400</v>
       </c>
       <c r="K11" t="n">
-        <v>32600</v>
+        <v>46350</v>
       </c>
       <c r="L11" t="n">
-        <v>32850</v>
+        <v>47850</v>
       </c>
       <c r="M11" t="n">
-        <v>30750</v>
+        <v>45650</v>
       </c>
       <c r="N11" t="n">
-        <v>10.77</v>
+        <v>14.1</v>
       </c>
       <c r="O11" t="n">
-        <v>48754723325</v>
+        <v>21379136400</v>
       </c>
       <c r="P11" t="n">
-        <v>75900</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>15960</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>-103000</v>
+        <v>-8000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>가온전선 대비 극심한 주가 부진 및 외국인/기관 매도세 지속. 소송 및 승계 작업 관련 루머.</t>
+          <t>FDA 승인 가능성 90% 이상 전망 및 담관암 매출 기대. 공매도 세력과의 갈등.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['가온전선', '외국인', '기관']</t>
+          <t>['FDA', '공매도', '담관암']</t>
         </is>
       </c>
       <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>30700</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-3.31%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" t="n">
+        <v>33</v>
+      </c>
+      <c r="G12" t="n">
+        <v>129</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>31750</v>
+      </c>
+      <c r="K12" t="n">
+        <v>32600</v>
+      </c>
+      <c r="L12" t="n">
+        <v>32850</v>
+      </c>
+      <c r="M12" t="n">
+        <v>30650</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="O12" t="n">
+        <v>53360552325</v>
+      </c>
+      <c r="P12" t="n">
+        <v>75900</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>15960</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-103000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>경쟁사 가온전선과의 비교, 주가 관리 미흡 지적.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['주가 관리', '경쟁사 비교']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>1</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>001440</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HLB제약</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12450</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-4.30%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E13" t="n">
+        <v>58</v>
+      </c>
+      <c r="F13" t="n">
+        <v>49</v>
+      </c>
+      <c r="G13" t="n">
+        <v>130</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>13010</v>
+      </c>
+      <c r="K13" t="n">
+        <v>12330</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13560</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12260</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>27106889355</v>
+      </c>
+      <c r="P13" t="n">
+        <v>22250</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-24000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>유증 물량 부담 및 주가 하락에 대한 우려.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['유상증자', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>047920</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261007_09.xlsx
+++ b/data/trending_integrated_20261007_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26500</v>
+        <v>26350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+15.47%</t>
+          <t>'+14.81%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="H2" t="n">
         <v>2.82</v>
@@ -610,7 +610,7 @@
         <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>54827897850</v>
+        <v>59479982750</v>
       </c>
       <c r="P2" t="n">
         <v>30100</v>
@@ -619,23 +619,23 @@
         <v>11140</v>
       </c>
       <c r="R2" t="n">
-        <v>141000</v>
+        <v>158000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-205000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>유리기판 관련 기술 및 주가 상승 기대감, 유상증자에 대한 논란.</t>
+          <t>유상증자 이슈 속에서 주가 상승 기대감이 공존하나, 투자 경고 및 하락 가능성에 대한 언급도 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['유리기판', '유상증자']</t>
+          <t>['유상증자', '주포', '유리기판']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5520</v>
+        <v>5390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.18%</t>
+          <t>'+7.58%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>3.32</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>4.72</v>
@@ -702,7 +702,7 @@
         <v>1.4</v>
       </c>
       <c r="O3" t="n">
-        <v>125355744635</v>
+        <v>135683927755</v>
       </c>
       <c r="P3" t="n">
         <v>8100</v>
@@ -711,14 +711,14 @@
         <v>592</v>
       </c>
       <c r="R3" t="n">
-        <v>908000</v>
+        <v>1405000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 수주 계약 규모 언급 및 기대감.</t>
+          <t>기타법인 자사주 매집 및 대규모 수주 계약 임박 공시에 대한 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매집', '수주 계약']</t>
+          <t>['자사주 매집', '수주 계약', '공시']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10560</v>
+        <v>10320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.20%</t>
+          <t>'+6.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.17</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="H4" t="n">
         <v>5.01</v>
@@ -788,13 +788,13 @@
         <v>11030</v>
       </c>
       <c r="M4" t="n">
-        <v>10420</v>
+        <v>10300</v>
       </c>
       <c r="N4" t="n">
         <v>4.84</v>
       </c>
       <c r="O4" t="n">
-        <v>8870044365</v>
+        <v>10348023205</v>
       </c>
       <c r="P4" t="n">
         <v>15900</v>
@@ -803,14 +803,14 @@
         <v>6310</v>
       </c>
       <c r="R4" t="n">
-        <v>-113000</v>
+        <v>-216000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>다양한 질병 테마주 언급, 페스트 확산 관련 소식.</t>
+          <t>신종 감염병 확산 가능성과 관련하여 테마주로서의 기대감이 있으나, 근거는 불확실.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['테마주', '질병 확산']</t>
+          <t>['신풍제약', '신종 감염병', '테마주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15870</v>
+        <v>15790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.72%</t>
+          <t>'+6.19%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H5" t="n">
         <v>2.37</v>
@@ -886,7 +886,7 @@
         <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>112110187605</v>
+        <v>118090282635</v>
       </c>
       <c r="P5" t="n">
         <v>16960</v>
@@ -895,14 +895,14 @@
         <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>-75000</v>
+        <v>-91000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>개인정보 유출 해킹 사건과 연관된 보안주 상승, 양자보안 기술 언급.</t>
+          <t>개인정보 유출 및 해킹 사고 발생에 따른 보안주 부각. 양자보안 기술력에 대한 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['해킹', '보안주']</t>
+          <t>['개인정보 유출', '양자보안', '보안주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>279000</v>
+        <v>278000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+2.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>661</v>
+        <v>718</v>
       </c>
       <c r="F6" t="n">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="G6" t="n">
-        <v>2059</v>
+        <v>2159</v>
       </c>
       <c r="H6" t="n">
         <v>46.37</v>
@@ -969,7 +969,7 @@
         <v>269500</v>
       </c>
       <c r="L6" t="n">
-        <v>279000</v>
+        <v>279500</v>
       </c>
       <c r="M6" t="n">
         <v>268500</v>
@@ -978,7 +978,7 @@
         <v>46.41</v>
       </c>
       <c r="O6" t="n">
-        <v>1022159316250</v>
+        <v>1229830070000</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -987,23 +987,23 @@
         <v>90200</v>
       </c>
       <c r="R6" t="n">
-        <v>359000</v>
+        <v>1232000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-121000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>이유 없는 하락 예측 및 정치적 언급.</t>
+          <t>정치적 이슈와 거시 경제 불확실성이 혼재하며, 단기적인 하락 가능성이 제기됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['자사주 매입', '환율', '실적 발표']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82200</v>
+        <v>82100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.86%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="F7" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G7" t="n">
-        <v>481</v>
+        <v>512</v>
       </c>
       <c r="H7" t="n">
         <v>22.59</v>
@@ -1070,7 +1070,7 @@
         <v>22.56</v>
       </c>
       <c r="O7" t="n">
-        <v>75084859550</v>
+        <v>80454778900</v>
       </c>
       <c r="P7" t="n">
         <v>139200</v>
@@ -1079,10 +1079,10 @@
         <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>143000</v>
+        <v>72000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-40000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242000</v>
+        <v>18530</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>1.11</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>512</v>
+        <v>599</v>
       </c>
       <c r="H8" t="n">
-        <v>4.12</v>
+        <v>4.92</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>241000</v>
+        <v>18530</v>
       </c>
       <c r="K8" t="n">
-        <v>253000</v>
+        <v>18950</v>
       </c>
       <c r="L8" t="n">
-        <v>257000</v>
+        <v>19870</v>
       </c>
       <c r="M8" t="n">
-        <v>235000</v>
+        <v>18360</v>
       </c>
       <c r="N8" t="n">
-        <v>4.08</v>
+        <v>3.81</v>
       </c>
       <c r="O8" t="n">
-        <v>52941309750</v>
+        <v>205336045745</v>
       </c>
       <c r="P8" t="n">
-        <v>1233000</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>120000</v>
+        <v>1272</v>
       </c>
       <c r="R8" t="n">
-        <v>-43000</v>
+        <v>-317000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 LO 예상 및 12월 임상 1차 결과 발표 예정. 아일리아 이슈와 더불어 외국인 수급 동향 주목.</t>
+          <t>미국 광통신 섹터 강세 및 젠슨황의 긍정적 발언에 따른 기대감. 프로그램 매매 주목.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['경구용 인슐린', '임상 1차', '외국인 수급']</t>
+          <t>['광통신', '젠슨황', '신고가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="G9" t="n">
-        <v>2143</v>
+        <v>2148</v>
       </c>
       <c r="H9" t="n">
         <v>49.71</v>
@@ -1254,7 +1254,7 @@
         <v>49.76</v>
       </c>
       <c r="O9" t="n">
-        <v>1207599985500</v>
+        <v>1371405525500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1263,23 +1263,23 @@
         <v>403000</v>
       </c>
       <c r="R9" t="n">
-        <v>-102000</v>
+        <v>-147000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-47000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>ADR 급락에 따른 주가 하락 우려, 외국인 매도세 지적.</t>
+          <t>미국 ADR 급락 영향으로 인한 한국 시장에서의 부정적 심리 확산. ADR 상장 이슈 부각.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['ADR', '외국인 매도']</t>
+          <t>['ADR', '급락', '락업 해제']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18480</v>
+        <v>236500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.27%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.11</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G10" t="n">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="H10" t="n">
-        <v>4.92</v>
+        <v>4.12</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18530</v>
+        <v>241000</v>
       </c>
       <c r="K10" t="n">
-        <v>18950</v>
+        <v>253000</v>
       </c>
       <c r="L10" t="n">
-        <v>19870</v>
+        <v>257000</v>
       </c>
       <c r="M10" t="n">
-        <v>18360</v>
+        <v>235000</v>
       </c>
       <c r="N10" t="n">
-        <v>3.81</v>
+        <v>4.08</v>
       </c>
       <c r="O10" t="n">
-        <v>196214983890</v>
+        <v>58173367500</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>1233000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1272</v>
+        <v>120000</v>
       </c>
       <c r="R10" t="n">
-        <v>49000</v>
+        <v>-43000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승 및 젠슨 황의 지지에 따른 기대감.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상 및 캐나다/독일 관련 호재 기대감. 다만, 외국인 수급 및 거래량 실림 등 일부 팩트 기반 언급 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '젠슨 황']</t>
+          <t>['경구용 인슐린', '공매도', 'L/O']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46100</v>
+        <v>45950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.74%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="F11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G11" t="n">
-        <v>1281</v>
+        <v>1354</v>
       </c>
       <c r="H11" t="n">
         <v>14.12</v>
@@ -1438,7 +1438,7 @@
         <v>14.1</v>
       </c>
       <c r="O11" t="n">
-        <v>21379136400</v>
+        <v>24213891750</v>
       </c>
       <c r="P11" t="n">
         <v>69200</v>
@@ -1447,23 +1447,23 @@
         <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>-8000</v>
+        <v>5000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상 전망 및 담관암 매출 기대. 공매도 세력과의 갈등.</t>
+          <t>FDA 승인 가능성 90% 이상에 기반한 높은 기대감. 공매도 세력과의 공방 속에 대규모 매출 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['FDA', '공매도', '담관암']</t>
+          <t>['FDA 승인', '공매도', '매출 전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="H12" t="n">
         <v>10.78</v>
@@ -1524,13 +1524,13 @@
         <v>32850</v>
       </c>
       <c r="M12" t="n">
-        <v>30650</v>
+        <v>30550</v>
       </c>
       <c r="N12" t="n">
         <v>10.77</v>
       </c>
       <c r="O12" t="n">
-        <v>53360552325</v>
+        <v>57583781625</v>
       </c>
       <c r="P12" t="n">
         <v>75900</v>
@@ -1539,14 +1539,14 @@
         <v>15960</v>
       </c>
       <c r="R12" t="n">
-        <v>-103000</v>
+        <v>-379000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-21000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>경쟁사 가온전선과의 비교, 주가 관리 미흡 지적.</t>
+          <t>경쟁사 대비 부진한 주가 흐름 및 주식 관리 부재에 대한 불만 토로. 기관/외인 매도세 확인.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가 관리', '경쟁사 비교']</t>
+          <t>['가온전선', '주가 관리', '기관 매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12450</v>
+        <v>12440</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.30%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1.88</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H13" t="n">
         <v>1.42</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>27106889355</v>
+        <v>28540779050</v>
       </c>
       <c r="P13" t="n">
         <v>22250</v>
@@ -1631,23 +1631,23 @@
         <v>6000</v>
       </c>
       <c r="R13" t="n">
-        <v>-24000</v>
+        <v>-100000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유증 물량 부담 및 주가 하락에 대한 우려.</t>
+          <t>유상증자 및 신규 상장 물량 부담으로 인한 하락세. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유상증자', '주가 하락']</t>
+          <t>['유상증자', '신규 상장', '주가 조작']</t>
         </is>
       </c>
       <c r="X13" t="n">
